--- a/report_forms/047_library_patron_incident_report_form--report_forms.xlsx
+++ b/report_forms/047_library_patron_incident_report_form--report_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,12 +1098,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="49" customWidth="1" min="2" max="2"/>
-    <col width="49" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'patron_behavior'}</t>
+          <t>patron_behavior</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Patron behavior'}</t>
+          <t>Patron behavior</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'patron_property_damage'}</t>
+          <t>patron_property_damage</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Patron property damage'}</t>
+          <t>Patron property damage</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'library_material_damage'}</t>
+          <t>library_material_damage</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Library material damage'}</t>
+          <t>Library material damage</t>
         </is>
       </c>
     </row>
@@ -1233,318 +1233,131 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'other_property_damage'}</t>
+          <t>other_property_damage</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Other property damage'}</t>
+          <t>Other property damage</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>incident_type_choices</t>
+          <t>follow_up_actions_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_6,_'label':_'other'}</t>
+          <t>send_a_note_to_the_patron</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 6, 'label': 'Other'}</t>
+          <t>Send a note to the patron</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>incident_type_choices</t>
+          <t>follow_up_actions_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_7,_'label':_'other'}</t>
+          <t>call_the_patron</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 7, 'label': 'Other'}</t>
+          <t>Call the patron</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>incident_type_choices</t>
+          <t>follow_up_actions_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_8,_'label':_'other'}</t>
+          <t>follow-up_meeting</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 8, 'label': 'Other'}</t>
+          <t>Follow-up meeting</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>incident_type_choices</t>
+          <t>follow_up_actions_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_9,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 9, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>follow_up_actions_choices</t>
+          <t>follow_up_contacts_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'send_a_note_to_the_patron'}</t>
+          <t>patron</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Send a note to the patron'}</t>
+          <t>Patron</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>follow_up_actions_choices</t>
+          <t>follow_up_contacts_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'call_the_patron'}</t>
+          <t>staff</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Call the patron'}</t>
+          <t>Staff</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>follow_up_actions_choices</t>
+          <t>follow_up_contacts_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'follow-up_meeting'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Follow-up meeting'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>follow_up_actions_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>{'id':_4,_'label':_'other'}</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>{'id': 4, 'label': 'Other'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>follow_up_actions_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>{'id':_5,_'label':_'other'}</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>{'id': 5, 'label': 'Other'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>follow_up_actions_choices</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>{'id':_6,_'label':_'other'}</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>{'id': 6, 'label': 'Other'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>follow_up_actions_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>{'id':_7,_'label':_'other'}</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>{'id': 7, 'label': 'Other'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>follow_up_contacts_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>{'id':_1,_'label':_'patron'}</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>{'id': 1, 'label': 'Patron'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>follow_up_contacts_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>{'id':_2,_'label':_'staff'}</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>{'id': 2, 'label': 'Staff'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>follow_up_contacts_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>{'id':_3,_'label':_'other'}</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>{'id': 3, 'label': 'Other'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>follow_up_contacts_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>{'id':_4,_'label':_'other'}</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>{'id': 4, 'label': 'Other'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>follow_up_contacts_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>{'id':_5,_'label':_'other'}</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>{'id': 5, 'label': 'Other'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>follow_up_contacts_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>{'id':_6,_'label':_'other'}</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>{'id': 6, 'label': 'Other'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>follow_up_contacts_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>{'id':_7,_'label':_'other'}</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>{'id': 7, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
